--- a/skills/qa/batch-qa-kerry/Kerry_Batch_QA_Checklist_Template.xlsx
+++ b/skills/qa/batch-qa-kerry/Kerry_Batch_QA_Checklist_Template.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kerry QA Checklist -- Template" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mangrove Routing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +50,30 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2D3D"/>
+    </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
+    <font>
+      <color rgb="00833C00"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00276221"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00833C00"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -69,8 +92,28 @@
         <bgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDCB5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -78,11 +121,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -98,6 +155,20 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1143,4 +1214,1498 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Section Name</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Automation / Review Notes</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Mangrove Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Batch Folder Completeness</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="11" t="n"/>
+      <c r="H2" s="10" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Batch Folder Completeness</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Batch folder exists with correct naming</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Pattern check</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Folder name matches Kerry batch ID format; auto-reject mismatches</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Charm Review Items</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Batch Folder Completeness</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Mass quantification subfolder present and populated (tote weighing or scale tickets per mode)</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Confirm weighing records exist for each tote or scale ticket pair for tanker mode</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Batch Folder Completeness</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Testing subfolder with all required SGS CHN lab results</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Per-tote CHN PDFs in tote mode; single CoA in tanker mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Batch Folder Completeness</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Ops Notes present and complete (Kerry mass IN, AECN mass IN, completion date, pH)</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>'Complete' requires reading the document; file presence alone insufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Mass Quantification</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Mass Quantification</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Per-tote weighing records present (gross, tare, net, serial, date, location) [TOTE MODE]</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Physical weighing records; confirm all fields populated for every tote</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Mass Quantification</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Tote tare is measured (not manufacturer nominal label) [TOTE MODE]</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Requires reading weighing records to confirm tare was measured on-site</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Mass Quantification</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Net mass calculation correct: (gross_lb − tare_lb) / 2.20462 per tote; sum = MOBI candidate</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Unit conversion + per-tote arithmetic + sum check; tolerance ±0.5 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Mass Quantification</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Scale ticket pair present and readable [TANKER MODE]</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Two images (empty + full) per truck; confirm legibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Mass Quantification</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Tractor/trailer numbers match between empty and full tickets [TANKER MODE]</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Requires reading equipment IDs from ticket images</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Mass Quantification</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Conservative MOBI: MIN(net candidate, BOL oil-only mass)</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Arithmetic / logic</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>MOBI = MIN(net_sum, BOL_oil_only); fail if higher value used as credit basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Mass Quantification</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Tote count reconciliation: count(BOL totes) = count(serials weighed) = count(Ops Notes) [TOTE MODE]</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Count match</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Three-way count equality; any mismatch = FC-K3 fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Mass Quantification</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Scale ticket dates within 2 weeks of injection [TANKER MODE]</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Date rule</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>abs(ticket_date − injection_date) ≤ 14 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>BOL &amp; Transportation</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>BOL &amp; Transportation</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>BOL(s) present for each shipment</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Confirm BOL PDF exists per shipment leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>BOL &amp; Transportation</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>BOL mass consistent with mass artifacts (tote: BOL gross ≥ MOBI + Σtare; tanker: BOL oil-only ≥ MOBI)</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Threshold check</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Mode-dependent inequality check; fail if MOBI exceeds BOL constraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>BOL &amp; Transportation</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Origin and destination correct on BOL: Kerry origin → Basco</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Requires reading origin/destination fields from BOL PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>BOL &amp; Transportation</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Transportation distance = 1,090 mi (current confirmed Kerry route)</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Lookup / reference</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>distance = 1090 mi; flag if any other value entered without documented justification</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Bio-Oil Composition &amp; Testing</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Bio-Oil Composition &amp; Testing</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>CHN analysis PDF(s) present (per-tote in tote mode; single CoA in tanker mode)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Confirm correct number of CHN PDFs for the delivery mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Bio-Oil Composition &amp; Testing</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Carbon content reported and used in Certify (FLAG-with-note until n ≥ ~30 samples for baseline)</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Statistical range</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>No Kerry baseline yet → auto-flag all C% entries; clear flag manually once baseline established</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Bio-Oil Composition &amp; Testing</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Lab report references correct batch/sample ID (per-tote serials match in tote mode)</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Requires reading lab PDF metadata; serial matching not yet structured</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Ops Notes Accuracy</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Ops Notes Accuracy</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Correct batch ID and injection date</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Cross-field match</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>ops_notes fields match canonical batch record</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Ops Notes Accuracy</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Mass values correctly transcribed: Kerry mass IN, AECN mass IN, total injectate</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Cross-field match</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>total_injectate = Kerry_IN + sparged_AECN_IN; fail on arithmetic mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Ops Notes Accuracy</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>COBB values present and match: consumed_lot (kc_NNNN pattern), origin_qty, BOL_number</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Cross-field match</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>COBB.consumed_lot matches kc_NNNN regex; COBB.origin_qty and BOL_number match Ops Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Ops Notes Accuracy</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Completion date present and matches COBB; pH noted in Batch Consumables</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Cross-field match</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>completion_date non-null and matches COBB; pH field non-null</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Gross-to-Net Calculation</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Gross-to-Net Calculation</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Gross CO2e = MOBI (un-sparged tonnes) × C% (decimal) × 3.667 — NO sparging deduction on Kerry mass (FC-K4)</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>gross = MOBI_t × (C_pct/100) × 3.667; verify no sparging deduction applied to Kerry portion</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Gross-to-Net Calculation</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Process emissions deducted: flatbed transport process+embodied; injection-site process+embodied only. NO upstream production components (FC-K5)</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>net_pre_unc = gross − transport_proc − transport_emb − injection_proc − injection_emb; upstream must be absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Gross-to-Net Calculation</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Uncertainty discount applied per Isometric Standard S3.7</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>net = net_pre_unc × (1 − uncertainty_rate) per Standard v2.0 S3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>6a</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Uncertainty Verification</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>6a</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Uncertainty Verification</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Layer 1 — Completeness: every Kerry component has uncertainty on correct datapoint</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Presence check</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Verify uncertainty field non-null per component type (Sequestration: Carbon Content + Mass of Product; Flatbed: Mass of Load; injection: per AECN convention)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>6a</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Uncertainty Verification</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Layer 2 — Correctness: ±1.13 kg per discrete weight; C content = 0.4% × measured value</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>uncertainty = N_totes × 1.13 kg (tote mode) or 1.13 kg (tanker mode); C_unc = 0.004 × C%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>6a</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Uncertainty Verification</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Layer 3 — Discount presence and consistency: net CDR calculation vs GHG Statement</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Cross-sheet match</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>certify_discount = GHG_stmt_discount; tolerance ±0.001 tCO2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Data Integrity &amp; Anomaly</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Data Integrity &amp; Anomaly</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>No unexplained outliers in mass, carbon content, or calculated values (FLAG-with-note until baseline exists)</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Statistical rule</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>No Kerry baseline yet → flag all outliers; require explanation field to clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Data Integrity &amp; Anomaly</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Spills/losses documented and unrecovered mass deducted; incident report filed</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Document reading</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Requires reading incident report and confirming deduction in mass calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>SEQUESTRATIONS: gross injection sequestration matches internal gross</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>certify_gross = internal_gross; tolerance ±0.001 tCO2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>ACTIVITIES — Transport: 2 components only (Flatbed Truck Process + Embodied); NOT tanker or railcar</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Presence check</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>Exactly 2 transport components; wrong mode present = fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>ACTIVITIES — Injection: electricity, pumping, embodied present</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>Presence check</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>All 3 injection components present with non-zero values</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>NO upstream production components for Kerry (waste boundary): Production Process and Production Embodied must be ABSENT (FC-K5)</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Absence check</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Kerry_Production_Process = absent; Kerry_Production_Embodied = absent; presence = FC-K5 fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>COUNTERFACTUALS: zero (waste boundary; non-zero = FC-K6 fail)</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Value check</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>counterfactual = 0; any non-zero entry = FC-K6 fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>REDUCTIONS: BCU Transport quantity ≥ flatbed process activity emission</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Threshold check</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>BCU_transport ≥ flatbed_process_emission; BCU cannot exceed actual emission</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Net removal matches independent gross-to-net calculation</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>Mangrove Rule</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>Cross-system match</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>certify_net = internal_net; tolerance ±0.001 tCO2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>All Datapoints have descriptive source names (no generic 'Measurement XXXX' or 'IMG_001')</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Judgment call</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Requires reading datapoint names; qualitative — needs human review</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Isometric Certify Mapping</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>All Sources in Certify match files in batch folder on Drive</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Charm Review</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Document inventory</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>Cross-reference Certify source list against Drive batch folder file inventory</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>